--- a/src/rattlesnake/examples/environment/sine/sine_v3.xlsx
+++ b/src/rattlesnake/examples/environment/sine/sine_v3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmlangs\Desktop\examples\environment\sine\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmlangs\Desktop\rattlesnake-vibration-controller-headless\src\rattlesnake\examples\environment\sine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D077EF-915A-4D46-8225-458CFB175B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A310632C-125B-4058-B45C-5DAF0724A101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6070" yWindow="1960" windowWidth="28790" windowHeight="15350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9610" yWindow="4200" windowWidth="28790" windowHeight="15350" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sine 0" sheetId="3" r:id="rId1"/>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
